--- a/data/trans_bre/DC-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/DC-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 14,05</t>
+          <t>0,84; 14,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 24,31</t>
+          <t>11,95; 24,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 21,59</t>
+          <t>8,69; 21,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,73</t>
+          <t>3,98; 14,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 133,49</t>
+          <t>4,55; 140,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>103,85; 402,95</t>
+          <t>106,92; 406,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,09; 280,51</t>
+          <t>61,33; 277,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 147,89</t>
+          <t>23,62; 154,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 28,18</t>
+          <t>17,18; 28,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,85</t>
+          <t>8,71; 17,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 8,28</t>
+          <t>1,14; 8,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 24,12</t>
+          <t>12,13; 23,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,04; 146,51</t>
+          <t>67,73; 150,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100,83; 351,54</t>
+          <t>86,75; 331,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 181,97</t>
+          <t>14,34; 190,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,99; 154,73</t>
+          <t>53,24; 147,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 16,58</t>
+          <t>5,67; 16,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,66</t>
+          <t>6,07; 17,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 15,63</t>
+          <t>5,92; 16,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 19,75</t>
+          <t>7,62; 19,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,67; 217,57</t>
+          <t>43,82; 224,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,96; 271,03</t>
+          <t>49,17; 252,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,1; 259,04</t>
+          <t>57,64; 272,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 102,25</t>
+          <t>30,26; 100,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,77</t>
+          <t>-4,13; 7,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 21,8</t>
+          <t>10,42; 21,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 19,09</t>
+          <t>8,01; 18,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 46,24</t>
+          <t>12,76; 50,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 45,28</t>
+          <t>-18,45; 43,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,68; 233,58</t>
+          <t>72,01; 243,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,05; 228,76</t>
+          <t>61,25; 237,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,73; 295,76</t>
+          <t>65,48; 337,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 18,6</t>
+          <t>5,47; 18,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,28; 30,8</t>
+          <t>14,01; 30,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 16,0</t>
+          <t>3,15; 16,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 18,12</t>
+          <t>-5,61; 18,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,54; 413,61</t>
+          <t>51,08; 422,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,67; 245,41</t>
+          <t>65,12; 230,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 193,4</t>
+          <t>17,18; 227,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 107,51</t>
+          <t>-24,28; 109,22</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 17,67</t>
+          <t>4,27; 17,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 18,45</t>
+          <t>4,95; 18,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 11,44</t>
+          <t>-0,85; 11,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,13; 21,98</t>
+          <t>9,19; 23,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,75; 140,5</t>
+          <t>19,31; 139,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 152,24</t>
+          <t>24,24; 149,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 157,24</t>
+          <t>-8,48; 164,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,25; 88,53</t>
+          <t>28,64; 94,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 8,38</t>
+          <t>-0,38; 7,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,95</t>
+          <t>10,26; 18,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,34</t>
+          <t>6,59; 14,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,58; 52,94</t>
+          <t>22,5; 53,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 57,11</t>
+          <t>-2,07; 54,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,13; 185,75</t>
+          <t>70,61; 184,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,91; 178,26</t>
+          <t>49,31; 164,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74,4; 194,6</t>
+          <t>70,8; 193,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 15,74</t>
+          <t>7,27; 16,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,46</t>
+          <t>5,9; 12,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 9,01</t>
+          <t>2,47; 9,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 28,1</t>
+          <t>12,46; 27,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,97; 77,09</t>
+          <t>28,9; 82,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,31; 172,78</t>
+          <t>57,54; 167,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,23; 110,92</t>
+          <t>19,9; 111,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,99; 413,83</t>
+          <t>63,74; 421,2</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,38</t>
+          <t>8,41; 12,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,19</t>
+          <t>11,77; 15,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,48</t>
+          <t>7,4; 10,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,76; 32,93</t>
+          <t>16,58; 32,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,37; 75,35</t>
+          <t>45,17; 74,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>103,9; 159,46</t>
+          <t>105,42; 160,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,34; 121,69</t>
+          <t>71,56; 121,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76,87; 186,06</t>
+          <t>78,21; 180,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DC-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/DC-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 14,03</t>
+          <t>0,56; 13,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 24,3</t>
+          <t>11,89; 24,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 21,76</t>
+          <t>8,39; 21,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,8</t>
+          <t>4,12; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 140,03</t>
+          <t>2,12; 126,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>106,92; 406,11</t>
+          <t>103,0; 400,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,33; 277,83</t>
+          <t>58,78; 265,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 154,4</t>
+          <t>26,59; 140,16</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,31</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,18; 28,28</t>
+          <t>16,83; 28,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 17,4</t>
+          <t>9,04; 17,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 8,61</t>
+          <t>1,67; 8,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,13; 23,31</t>
+          <t>11,87; 22,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,73; 150,41</t>
+          <t>67,22; 148,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,75; 331,68</t>
+          <t>96,38; 351,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 190,53</t>
+          <t>20,11; 187,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,24; 147,96</t>
+          <t>52,02; 139,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 16,63</t>
+          <t>5,64; 16,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 17,05</t>
+          <t>6,27; 17,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 16,18</t>
+          <t>5,39; 16,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 19,95</t>
+          <t>9,2; 20,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,82; 224,38</t>
+          <t>42,63; 226,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,17; 252,44</t>
+          <t>54,84; 282,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,64; 272,7</t>
+          <t>50,66; 262,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,26; 100,51</t>
+          <t>34,15; 105,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,02</t>
+          <t>19,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>142,86%</t>
+          <t>125,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 7,39</t>
+          <t>-3,85; 7,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 21,62</t>
+          <t>10,27; 21,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 18,93</t>
+          <t>7,93; 19,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 50,33</t>
+          <t>13,55; 25,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 43,39</t>
+          <t>-16,41; 47,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,01; 243,05</t>
+          <t>68,39; 235,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,25; 237,99</t>
+          <t>63,23; 226,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,48; 337,17</t>
+          <t>64,57; 200,44</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>15,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 18,85</t>
+          <t>5,91; 18,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,01; 30,78</t>
+          <t>14,39; 31,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 16,91</t>
+          <t>1,41; 15,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 18,33</t>
+          <t>9,06; 22,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,08; 422,26</t>
+          <t>55,47; 382,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,12; 230,6</t>
+          <t>68,11; 253,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 227,74</t>
+          <t>5,9; 201,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 109,22</t>
+          <t>40,12; 155,77</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>15,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,82</t>
+          <t>2,38; 17,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,96</t>
+          <t>3,92; 18,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 11,54</t>
+          <t>-0,04; 11,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 23,37</t>
+          <t>8,96; 21,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,31; 139,55</t>
+          <t>10,1; 125,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,24; 149,53</t>
+          <t>18,89; 144,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 164,51</t>
+          <t>-3,42; 156,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,64; 94,0</t>
+          <t>27,85; 87,78</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,65</t>
+          <t>25,72</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>114,54%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 7,92</t>
+          <t>-0,44; 8,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,26; 18,87</t>
+          <t>10,01; 18,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,9</t>
+          <t>6,78; 14,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,5; 53,68</t>
+          <t>20,58; 30,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 54,83</t>
+          <t>-2,74; 58,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,61; 184,13</t>
+          <t>68,28; 182,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,31; 164,18</t>
+          <t>50,31; 164,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,8; 193,18</t>
+          <t>59,42; 110,05</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,59</t>
+          <t>13,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>132,19%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,42</t>
+          <t>6,86; 15,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,23</t>
+          <t>5,89; 12,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,16</t>
+          <t>2,33; 9,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,46; 27,85</t>
+          <t>9,74; 17,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,9; 82,19</t>
+          <t>27,86; 79,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,54; 167,73</t>
+          <t>55,61; 172,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,9; 111,03</t>
+          <t>21,14; 117,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,74; 421,2</t>
+          <t>48,21; 106,94</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22,16</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>109,71%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,31</t>
+          <t>8,42; 12,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,77; 15,3</t>
+          <t>11,67; 15,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,77</t>
+          <t>7,18; 10,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,58; 32,31</t>
+          <t>15,32; 19,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,17; 74,5</t>
+          <t>45,86; 73,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105,42; 160,14</t>
+          <t>104,6; 158,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,56; 121,28</t>
+          <t>69,92; 122,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78,21; 180,52</t>
+          <t>67,67; 94,67</t>
         </is>
       </c>
     </row>
